--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N75_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.589560771067</v>
+        <v>10.82080362529839</v>
       </c>
       <c r="D2" t="n">
-        <v>66.382564219191</v>
+        <v>10.78716668561854</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
